--- a/artfynd/A 42388-2025 artfynd.xlsx
+++ b/artfynd/A 42388-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129603817</v>
       </c>
       <c r="B2" t="n">
-        <v>92847</v>
+        <v>92875</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129605929</v>
       </c>
       <c r="B3" t="n">
-        <v>91564</v>
+        <v>91592</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42388-2025 artfynd.xlsx
+++ b/artfynd/A 42388-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129603817</v>
       </c>
       <c r="B2" t="n">
-        <v>92875</v>
+        <v>92881</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129605929</v>
       </c>
       <c r="B3" t="n">
-        <v>91592</v>
+        <v>91598</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42388-2025 artfynd.xlsx
+++ b/artfynd/A 42388-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129603817</v>
       </c>
       <c r="B2" t="n">
-        <v>92881</v>
+        <v>92882</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129605929</v>
       </c>
       <c r="B3" t="n">
-        <v>91598</v>
+        <v>91599</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42388-2025 artfynd.xlsx
+++ b/artfynd/A 42388-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129603817</v>
       </c>
       <c r="B2" t="n">
-        <v>92882</v>
+        <v>92887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129605929</v>
       </c>
       <c r="B3" t="n">
-        <v>91599</v>
+        <v>91604</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42388-2025 artfynd.xlsx
+++ b/artfynd/A 42388-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129603817</v>
       </c>
       <c r="B2" t="n">
-        <v>92887</v>
+        <v>92891</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129605929</v>
       </c>
       <c r="B3" t="n">
-        <v>91604</v>
+        <v>91608</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42388-2025 artfynd.xlsx
+++ b/artfynd/A 42388-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129603817</v>
       </c>
       <c r="B2" t="n">
-        <v>92891</v>
+        <v>92893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129605929</v>
       </c>
       <c r="B3" t="n">
-        <v>91608</v>
+        <v>91610</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42388-2025 artfynd.xlsx
+++ b/artfynd/A 42388-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129603817</v>
       </c>
       <c r="B2" t="n">
-        <v>92893</v>
+        <v>92896</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129605929</v>
       </c>
       <c r="B3" t="n">
-        <v>91610</v>
+        <v>91613</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42388-2025 artfynd.xlsx
+++ b/artfynd/A 42388-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129603817</v>
       </c>
       <c r="B2" t="n">
-        <v>92896</v>
+        <v>92899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129605929</v>
       </c>
       <c r="B3" t="n">
-        <v>91613</v>
+        <v>91616</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42388-2025 artfynd.xlsx
+++ b/artfynd/A 42388-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129603817</v>
+        <v>129605929</v>
       </c>
       <c r="B2" t="n">
-        <v>92899</v>
+        <v>91920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bjursjön, Bjursjön, Ög</t>
+          <t>Övergivern/näset , Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555137</v>
+        <v>554978</v>
       </c>
       <c r="R2" t="n">
-        <v>6512421</v>
+        <v>6512362</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,19 +750,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,6 +761,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,52 +780,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129605929</v>
+        <v>129603817</v>
       </c>
       <c r="B3" t="n">
-        <v>91616</v>
+        <v>93209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1205</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Övergivern/näset , Ög</t>
+          <t>Bjursjön, Bjursjön, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>554978</v>
+        <v>555137</v>
       </c>
       <c r="R3" t="n">
-        <v>6512362</v>
+        <v>6512421</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,9 +848,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -868,7 +869,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42388-2025 artfynd.xlsx
+++ b/artfynd/A 42388-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129605929</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,8 +894,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129603817</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>